--- a/tests/testdata/excel/混在/同名.xlsx
+++ b/tests/testdata/excel/混在/同名.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{830B1CED-07DB-433C-9901-514F434934CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD65672-6587-4A0D-B11F-44EA35971EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{94F13A38-EC4B-465A-84AD-DCCA44399EF2}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{6B3DEF2D-CA3E-4A1A-A0A2-312588877402}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12AA2FD-3945-461B-A1D9-252FED796B66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB7A1C6-0525-47EF-9EF5-2541EF783B1F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
